--- a/Templates~/Config/Excels/L10n/LocalizedStrings.xlsx
+++ b/Templates~/Config/Excels/L10n/LocalizedStrings.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workspace\Unity\Game Dev Tools\Packages\com.moirai.framework\Templates~\Config\Excels\L10n\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workspace\Unity\Game Dev Tools\Config\Excels\L10n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D993B1-36B9-43A7-AF19-236C2315E7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB8FB14-F027-4AD7-8EB2-9BAD5B45232A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4635" yWindow="4635" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4980" yWindow="4980" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -141,10 +141,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>L10n.LocalizedStringBean</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>zh-Hans</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -178,6 +174,10 @@
   </si>
   <si>
     <t>Test</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L10n.LocalizedBean</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -303,7 +303,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -322,9 +322,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -620,7 +617,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D1" s="6"/>
     </row>
@@ -632,7 +629,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D2" s="6"/>
     </row>
@@ -642,10 +639,10 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -666,7 +663,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" s="6"/>
     </row>
@@ -675,7 +672,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -683,22 +680,22 @@
         <v>9</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="9" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="7"/>
+      <c r="B9" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="B1:B7" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Templates~/Config/Excels/L10n/LocalizedStrings.xlsx
+++ b/Templates~/Config/Excels/L10n/LocalizedStrings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workspace\Unity\Game Dev Tools\Config\Excels\L10n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB8FB14-F027-4AD7-8EB2-9BAD5B45232A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E02985-1C54-4AC3-AAE5-ADD32110455F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4980" yWindow="4980" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -177,7 +177,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>L10n.LocalizedBean</t>
+    <t>L10n.LocalizationBean</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
